--- a/doc/help_dialogs/Input_files/symbolic.xlsx
+++ b/doc/help_dialogs/Input_files/symbolic.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Symbolic Variables" sheetId="1" state="visible" r:id="rId3"/>
@@ -37,25 +37,7 @@
     <t xml:space="preserve">SYMBOLIC VARIABLES</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">tn:Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">All symbolic variables are case sensitive!</t>
-    </r>
+    <t xml:space="preserve">tn:Note: All symbolic variables are case sensitive!</t>
   </si>
   <si>
     <t xml:space="preserve">Symbol</t>
@@ -310,13 +292,13 @@
     <t xml:space="preserve">k</t>
   </si>
   <si>
-    <t xml:space="preserve">Scaling factor from RoR to Temp axis. The range of the temperature scale divided by the range of the delta scale. </t>
+    <t xml:space="preserve">Scaling factor from RoR to Temp axis. The range of the temperature scale divided by the range of the delta scale.</t>
   </si>
   <si>
     <t xml:space="preserve">o</t>
   </si>
   <si>
-    <t xml:space="preserve">Offset from RoR to Temp axis. </t>
+    <t xml:space="preserve">Offset from RoR to Temp axis.</t>
   </si>
   <si>
     <t xml:space="preserve">bn:Note: RoR values r can be scaled to the temperature axis using a linear approximation of the form "r*k + o". As the variables k and o depend on the actual axis settings which can be changed by the user without triggering a recomputation, those variable are less useful for use in a recording, but useful in the Plotter to plot w.r.t. the RoR y-axis instead of the temperature y-axis.</t>
@@ -590,7 +572,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -612,12 +594,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -713,60 +689,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1022,347 +1002,347 @@
   <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="59.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="59.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="C20" s="3"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="C21" s="3"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="3"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="2"/>
+      <c r="C24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="2"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="2"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="2"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1385,27 +1365,27 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>132</v>
       </c>
     </row>
@@ -1428,148 +1408,148 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="11" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="11" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="11" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="11" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="33.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="11" t="s">
         <v>166</v>
       </c>
     </row>
@@ -1593,31 +1573,31 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2.71828182845904</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>3.14159265358979</v>
       </c>
     </row>
@@ -1641,36 +1621,36 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>176</v>
       </c>
     </row>
@@ -1693,87 +1673,87 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="8"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="11" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="13" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1797,23 +1777,23 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1836,41 +1816,41 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1894,39 +1874,39 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1950,39 +1930,39 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2006,56 +1986,56 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2079,44 +2059,44 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2140,39 +2120,39 @@
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
